--- a/consent_forms/040_voice_sample_portfolio_release_consent_form--consent_forms.xlsx
+++ b/consent_forms/040_voice_sample_portfolio_release_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>title_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date Signed</t>
+          <t>Date Signed Consent</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Signed By</t>
+          <t>Name Signed Con</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature Signed</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Signed Con</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Contact Phone Signed</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Address Signed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Company Signed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Title Signed</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category',_'label':_'category'}</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category', 'label': 'Category'}</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -1152,233 +1152,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category',_'label':_'category'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category', 'label': 'Category'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category',_'label':_'category'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Category', 'label': 'Category'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'category',_'label':_'category'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Category', 'label': 'Category'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>consent_signed_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'category',_'label':_'category'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Category', 'label': 'Category'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>consent_signed_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'name':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_6,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 6, 'name': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_7,_'name':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 7, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_8,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 8, 'name': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>consent_signed_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>consent_signed_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
